--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127702798</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127702798</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127702798</v>
       </c>
       <c r="B3" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33908-2025 artfynd.xlsx
+++ b/artfynd/A 33908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127702631</v>
       </c>
       <c r="B2" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127702798</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127702428</v>
       </c>
       <c r="B4" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
